--- a/cl_st3_ph1_eyamrog/df_section_paragraph.xlsx
+++ b/cl_st3_ph1_eyamrog/df_section_paragraph.xlsx
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Linguistic, literature and arts</t>
+          <t>Linguistics, Literature, and Arts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
